--- a/InputData/trans/BVTQaZ/BAU Veh Techs Qualifying as ZEVs.xlsx
+++ b/InputData/trans/BVTQaZ/BAU Veh Techs Qualifying as ZEVs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BVTQaZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\CO\trans\BVTQaZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D6E708-877B-4EA5-8B13-7CB340C7CC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB7DC730-4E9E-4185-A527-1CC76FFF320D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{7166B4F5-29DF-47A7-8501-7E54D22AC689}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7166B4F5-29DF-47A7-8501-7E54D22AC689}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="12">
   <si>
     <t>Source:</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>BVTQaZ BAU Vehicle Technologies Qualifying as ZEVs</t>
+  </si>
+  <si>
+    <t>Colorado</t>
   </si>
 </sst>
 </file>
@@ -126,10 +129,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,15 +448,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C5140B-A3FA-4DAF-B6D3-27BA9BD40705}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3">
+        <v>46184</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,12 +482,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -575,7 +585,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -673,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -771,7 +781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -869,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -967,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1065,7 +1075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1163,7 +1173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1272,12 +1282,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -1375,7 +1385,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1473,7 +1483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1571,7 +1581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1669,7 +1679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1767,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1865,7 +1875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1963,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -2072,12 +2082,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2175,7 +2185,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2273,7 +2283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2371,7 +2381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2469,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2567,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2665,7 +2675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2763,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -2872,12 +2882,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -2975,7 +2985,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3073,7 +3083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3171,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3269,7 +3279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -3367,7 +3377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -3465,7 +3475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3563,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -3672,12 +3682,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -3775,7 +3785,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3873,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3971,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -4069,7 +4079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4167,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -4265,7 +4275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -4363,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -4472,12 +4482,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -4575,7 +4585,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4673,7 +4683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -4771,7 +4781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -4869,7 +4879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4967,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -5065,7 +5075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -5163,7 +5173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>2</v>
       </c>
